--- a/univTest.xlsx
+++ b/univTest.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12255"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12255" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Standard" sheetId="2" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="636" uniqueCount="492">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="854" uniqueCount="517">
   <si>
     <t>가천길병원</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -158,9 +158,6 @@
     <t>한국농수산대학</t>
   </si>
   <si>
-    <t>국립암센터국제암대학원대학교</t>
-  </si>
-  <si>
     <t>경북대학교병원</t>
   </si>
   <si>
@@ -191,1487 +188,1582 @@
     <t>강북삼성병원</t>
   </si>
   <si>
+    <t>경일대학교</t>
+  </si>
+  <si>
+    <t>가톨릭관동대국제성모병원</t>
+  </si>
+  <si>
+    <t>서울여자대학교</t>
+  </si>
+  <si>
+    <t>중앙대학교광명병원</t>
+  </si>
+  <si>
+    <t>강원대학교 춘천캠퍼스</t>
+  </si>
+  <si>
+    <t>연세대학교 미래캠퍼스</t>
+  </si>
+  <si>
+    <t>강릉원주대학교</t>
+  </si>
+  <si>
+    <t>중부대학교</t>
+  </si>
+  <si>
+    <t>서울교육대학교</t>
+  </si>
+  <si>
+    <t>안양대학교</t>
+  </si>
+  <si>
+    <t>계명대학교 동산의료원</t>
+  </si>
+  <si>
+    <t>강원대학교병원</t>
+  </si>
+  <si>
+    <t>신한대학교</t>
+  </si>
+  <si>
+    <t>동서대학교</t>
+  </si>
+  <si>
+    <t>대구보건대학교</t>
+  </si>
+  <si>
+    <t>백석대학교</t>
+  </si>
+  <si>
+    <t>경민대학교</t>
+  </si>
+  <si>
+    <t>강남대학교</t>
+  </si>
+  <si>
+    <t>국립중앙의료원</t>
+  </si>
+  <si>
+    <t>부산가톨릭대학교</t>
+  </si>
+  <si>
+    <t>인제대학교 부산백병원</t>
+  </si>
+  <si>
+    <t>서울미디어대학원대학교</t>
+  </si>
+  <si>
+    <t>고신대학교</t>
+  </si>
+  <si>
+    <t>성결대학교</t>
+  </si>
+  <si>
+    <t>충북도립대학교</t>
+  </si>
+  <si>
+    <t>한세대학교</t>
+  </si>
+  <si>
+    <t>나사렛대학교</t>
+  </si>
+  <si>
+    <t>한국뉴육주립대학교</t>
+  </si>
+  <si>
+    <t>한림국제대학원대학교</t>
+  </si>
+  <si>
+    <t>육군사관학교</t>
+  </si>
+  <si>
+    <t>남부대학교</t>
+  </si>
+  <si>
+    <t>창신대학교</t>
+  </si>
+  <si>
+    <t>㈜에이치에스씨엠티</t>
+  </si>
+  <si>
+    <t>서울예술대학교</t>
+  </si>
+  <si>
+    <t>경동대학교</t>
+  </si>
+  <si>
+    <t>태재대학교</t>
+  </si>
+  <si>
+    <t>국방대학교</t>
+  </si>
+  <si>
+    <t>극동대학교</t>
+  </si>
+  <si>
+    <t>경찰대학교</t>
+  </si>
+  <si>
+    <t>SANRPM002</t>
+  </si>
+  <si>
+    <t>SANRPM003</t>
+  </si>
+  <si>
+    <t>SANRPM005</t>
+  </si>
+  <si>
+    <t>SANRPM006</t>
+  </si>
+  <si>
+    <t>SANRPM007</t>
+  </si>
+  <si>
+    <t>SANRPM008</t>
+  </si>
+  <si>
+    <t>SANRPM010</t>
+  </si>
+  <si>
+    <t>SANRPM011</t>
+  </si>
+  <si>
+    <t>SANRPM012</t>
+  </si>
+  <si>
+    <t>SANRPM016</t>
+  </si>
+  <si>
+    <t>SANRPM018</t>
+  </si>
+  <si>
+    <t>SANRPM019</t>
+  </si>
+  <si>
+    <t>SANRPM020</t>
+  </si>
+  <si>
+    <t>SANRPM021</t>
+  </si>
+  <si>
+    <t>SANRPM026</t>
+  </si>
+  <si>
+    <t>SANRPM029</t>
+  </si>
+  <si>
+    <t>SANRPM030</t>
+  </si>
+  <si>
+    <t>SANRPM036</t>
+  </si>
+  <si>
+    <t>SANRPM037</t>
+  </si>
+  <si>
+    <t>SANRPM038</t>
+  </si>
+  <si>
+    <t>SANRPM047</t>
+  </si>
+  <si>
+    <t>SANRPM048</t>
+  </si>
+  <si>
+    <t>SANRPM049</t>
+  </si>
+  <si>
+    <t>SANRPM050</t>
+  </si>
+  <si>
+    <t>SANRPM052</t>
+  </si>
+  <si>
+    <t>SANRPM054</t>
+  </si>
+  <si>
+    <t>SANRPM055</t>
+  </si>
+  <si>
+    <t>SANRPM057</t>
+  </si>
+  <si>
+    <t>SANRPM058</t>
+  </si>
+  <si>
+    <t>SANRPM062</t>
+  </si>
+  <si>
+    <t>SANRPM065</t>
+  </si>
+  <si>
+    <t>SMARTRND_008</t>
+  </si>
+  <si>
+    <t>SMARTRND_010</t>
+  </si>
+  <si>
+    <t>SMARTRND_012</t>
+  </si>
+  <si>
+    <t>SMARTRND_015</t>
+  </si>
+  <si>
+    <t>SANRPM009</t>
+  </si>
+  <si>
+    <t>SANRPM014</t>
+  </si>
+  <si>
+    <t>SANRPM015</t>
+  </si>
+  <si>
+    <t>SANRPM017</t>
+  </si>
+  <si>
+    <t>SANRPM013</t>
+  </si>
+  <si>
+    <t>SANRPM022</t>
+  </si>
+  <si>
+    <t>SANRPM023</t>
+  </si>
+  <si>
+    <t>SANRPM024</t>
+  </si>
+  <si>
+    <t>SANRPM025</t>
+  </si>
+  <si>
+    <t>SANRPM027</t>
+  </si>
+  <si>
+    <t>SANRPM028</t>
+  </si>
+  <si>
+    <t>SANRPM031</t>
+  </si>
+  <si>
+    <t>SANRPM032</t>
+  </si>
+  <si>
+    <t>SANRPM034</t>
+  </si>
+  <si>
+    <t>SANRPM035</t>
+  </si>
+  <si>
+    <t>SANRPM039</t>
+  </si>
+  <si>
+    <t>SANRPM040</t>
+  </si>
+  <si>
+    <t>SANRPM041</t>
+  </si>
+  <si>
+    <t>SANRPM042</t>
+  </si>
+  <si>
+    <t>SANRPM043</t>
+  </si>
+  <si>
+    <t>SANRPM044</t>
+  </si>
+  <si>
+    <t>SANRPM045</t>
+  </si>
+  <si>
+    <t>SANRPM046</t>
+  </si>
+  <si>
+    <t>SANRPM051</t>
+  </si>
+  <si>
+    <t>SANRPM053</t>
+  </si>
+  <si>
+    <t>SANRPM056</t>
+  </si>
+  <si>
+    <t>SANRPM059</t>
+  </si>
+  <si>
+    <t>SANRPM060</t>
+  </si>
+  <si>
+    <t>SANRPM061</t>
+  </si>
+  <si>
+    <t>SANRPM063</t>
+  </si>
+  <si>
+    <t>SANRPM064</t>
+  </si>
+  <si>
+    <t>SANRPM066</t>
+  </si>
+  <si>
+    <t>SANRPM067</t>
+  </si>
+  <si>
+    <t>SANRPM068</t>
+  </si>
+  <si>
+    <t>SANRPM069</t>
+  </si>
+  <si>
+    <t>SANRPM070</t>
+  </si>
+  <si>
+    <t>SANRPM071</t>
+  </si>
+  <si>
+    <t>SANRPM072</t>
+  </si>
+  <si>
+    <t>SANRPM073</t>
+  </si>
+  <si>
+    <t>SANRPM074</t>
+  </si>
+  <si>
+    <t>SANRPM_ADMIN</t>
+  </si>
+  <si>
+    <t>SMARTRND</t>
+  </si>
+  <si>
+    <t>SMARTRND_001</t>
+  </si>
+  <si>
+    <t>SMARTRND_003</t>
+  </si>
+  <si>
+    <t>SMARTRND_004</t>
+  </si>
+  <si>
+    <t>SMARTRND_005</t>
+  </si>
+  <si>
+    <t>SMARTRND_006</t>
+  </si>
+  <si>
+    <t>SMARTRND_009</t>
+  </si>
+  <si>
+    <t>SMARTRND_011</t>
+  </si>
+  <si>
+    <t>SMARTRND_013</t>
+  </si>
+  <si>
+    <t>SMARTRND_014</t>
+  </si>
+  <si>
+    <t>SMARTRND_016</t>
+  </si>
+  <si>
+    <t>SMARTRND_017</t>
+  </si>
+  <si>
+    <t>SMARTRND_018</t>
+  </si>
+  <si>
+    <t>SMARTRND_019</t>
+  </si>
+  <si>
+    <t>SMARTRND_020</t>
+  </si>
+  <si>
+    <t>SMARTRND_021</t>
+  </si>
+  <si>
+    <t>SANRpm_proj2</t>
+  </si>
+  <si>
+    <t>SANRpm_proj3</t>
+  </si>
+  <si>
+    <t>SANRpm_proj5</t>
+  </si>
+  <si>
+    <t>SANRpm_proj6</t>
+  </si>
+  <si>
+    <t>SANRpm_proj7</t>
+  </si>
+  <si>
+    <t>SANRpm_proj8</t>
+  </si>
+  <si>
+    <t>SANRpm_proj10</t>
+  </si>
+  <si>
+    <t>SANRpm_proj11</t>
+  </si>
+  <si>
+    <t>SANRpm_proj12</t>
+  </si>
+  <si>
+    <t>SANRpm_proj16</t>
+  </si>
+  <si>
+    <t>SANRpm_proj17</t>
+  </si>
+  <si>
+    <t>SANRpm_proj25</t>
+  </si>
+  <si>
+    <t>SANRpm_proj26</t>
+  </si>
+  <si>
+    <t>SANRpm_proj36</t>
+  </si>
+  <si>
+    <t>SANRpm_proj37</t>
+  </si>
+  <si>
+    <t>SANRpm_proj38</t>
+  </si>
+  <si>
+    <t>SANRpm_proj42</t>
+  </si>
+  <si>
+    <t>SANRpm_proj47</t>
+  </si>
+  <si>
+    <t>SANRpm_proj48</t>
+  </si>
+  <si>
+    <t>SANRpm_proj49</t>
+  </si>
+  <si>
+    <t>SANRpm_proj50</t>
+  </si>
+  <si>
+    <t>SANRpm_proj52</t>
+  </si>
+  <si>
+    <t>SANRpm_proj53</t>
+  </si>
+  <si>
+    <t>SANRpm_proj54</t>
+  </si>
+  <si>
+    <t>SANRpm_proj55</t>
+  </si>
+  <si>
+    <t>SANRpm_proj56</t>
+  </si>
+  <si>
+    <t>SANRpm_proj57</t>
+  </si>
+  <si>
+    <t>SANRpm_proj58</t>
+  </si>
+  <si>
+    <t>SANRpm_proj62</t>
+  </si>
+  <si>
+    <t>SANRpm_proj63</t>
+  </si>
+  <si>
+    <t>SANRpm_proj64</t>
+  </si>
+  <si>
+    <t>SANRpm_proj65</t>
+  </si>
+  <si>
+    <t>Srnd_proj8</t>
+  </si>
+  <si>
+    <t>Srnd_proj9</t>
+  </si>
+  <si>
+    <t>Srnd_proj10</t>
+  </si>
+  <si>
+    <t>Srnd_proj12</t>
+  </si>
+  <si>
+    <t>Srnd_proj15</t>
+  </si>
+  <si>
+    <t>SANRpm_proj9</t>
+  </si>
+  <si>
+    <t>SANRpm_proj14</t>
+  </si>
+  <si>
+    <t>SANRpm_proj15</t>
+  </si>
+  <si>
+    <t>SANRpm_proj18</t>
+  </si>
+  <si>
+    <t>SANRpm_proj19</t>
+  </si>
+  <si>
+    <t>SANRpm_proj20</t>
+  </si>
+  <si>
+    <t>SANRpm_proj21</t>
+  </si>
+  <si>
+    <t>SANRpm_proj13</t>
+  </si>
+  <si>
+    <t>SANRpm_Admin</t>
+  </si>
+  <si>
+    <t>SANRpm_proj22</t>
+  </si>
+  <si>
+    <t>SANRpm_proj23</t>
+  </si>
+  <si>
+    <t>SANRpm_proj24</t>
+  </si>
+  <si>
+    <t>SANRpm_proj27</t>
+  </si>
+  <si>
+    <t>SANRpm_proj28</t>
+  </si>
+  <si>
+    <t>SANRpm_proj29</t>
+  </si>
+  <si>
+    <t>SANRpm_proj30</t>
+  </si>
+  <si>
+    <t>SANRpm_proj31</t>
+  </si>
+  <si>
+    <t>SANRpm_proj32</t>
+  </si>
+  <si>
+    <t>SANRpm_proj34</t>
+  </si>
+  <si>
+    <t>SANRpm_proj35</t>
+  </si>
+  <si>
+    <t>SANRpm_proj39</t>
+  </si>
+  <si>
+    <t>SANRpm_proj40</t>
+  </si>
+  <si>
+    <t>SANRpm_proj41</t>
+  </si>
+  <si>
+    <t>SANRpm_proj43</t>
+  </si>
+  <si>
+    <t>SANRpm_proj44</t>
+  </si>
+  <si>
+    <t>SANRpm_proj45</t>
+  </si>
+  <si>
+    <t>SANRpm_proj46</t>
+  </si>
+  <si>
+    <t>SANRpm_proj51</t>
+  </si>
+  <si>
+    <t>SANRpm_proj59</t>
+  </si>
+  <si>
+    <t>SANRpm_proj60</t>
+  </si>
+  <si>
+    <t>SANRpm_proj61</t>
+  </si>
+  <si>
+    <t>SANRpm_proj66</t>
+  </si>
+  <si>
+    <t>SANRpm_proj67</t>
+  </si>
+  <si>
+    <t>SANRpm_proj68</t>
+  </si>
+  <si>
+    <t>SANRpm_proj69</t>
+  </si>
+  <si>
+    <t>SANRpm_proj70</t>
+  </si>
+  <si>
+    <t>SANRpm_proj71</t>
+  </si>
+  <si>
+    <t>SANRpm_proj72</t>
+  </si>
+  <si>
+    <t>SANRpm_proj73</t>
+  </si>
+  <si>
+    <t>SANRpm_proj74</t>
+  </si>
+  <si>
+    <t>SANRpm_proj75</t>
+  </si>
+  <si>
+    <t>Srnd_project</t>
+  </si>
+  <si>
+    <t>Srnd_proj1</t>
+  </si>
+  <si>
+    <t>Srnd_proj2</t>
+  </si>
+  <si>
+    <t>Srnd_proj3</t>
+  </si>
+  <si>
+    <t>Srnd_proj4</t>
+  </si>
+  <si>
+    <t>Srnd_proj5</t>
+  </si>
+  <si>
+    <t>Srnd_proj6</t>
+  </si>
+  <si>
+    <t>Srnd_proj11</t>
+  </si>
+  <si>
+    <t>Srnd_proj13</t>
+  </si>
+  <si>
+    <t>Srnd_proj14</t>
+  </si>
+  <si>
+    <t>Srnd_proj16</t>
+  </si>
+  <si>
+    <t>Srnd_proj17</t>
+  </si>
+  <si>
+    <t>Srnd_proj18</t>
+  </si>
+  <si>
+    <t>Srnd_proj19</t>
+  </si>
+  <si>
+    <t>Srnd_proj20</t>
+  </si>
+  <si>
+    <t>Srnd_proj21</t>
+  </si>
+  <si>
+    <t>홍익대</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>교통대</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>한밭대</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>충남대</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공주대</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>인천대</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>해양대</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>동의대</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>인제대</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>한남대</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>호서대</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>군산대</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>경남대</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>금오공대</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>경상대</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가천대</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>명지대</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>한기대</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>한림대</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>항공대</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>건양대</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>충북대병원</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>건국대</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>부경대</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>부산대</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>강원대</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전남대</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>남서울대</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>서경대</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>차의과대</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>세종대</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>대구가톨릭대</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>국립경국대</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>한국외대</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>한경대</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>숙명여대</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기관명</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DB</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WAS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>구분</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>URL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SERVER2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SERVER1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SaaS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Standard</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>구분</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기관명</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>URL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://sanhak.hongik.ac.kr/</t>
+  </si>
+  <si>
+    <t>https://sanhak-erp.ut.ac.kr/</t>
+  </si>
+  <si>
+    <t>https://rnd.hanbat.ac.kr/</t>
+  </si>
+  <si>
+    <t>https://forb.cnu.ac.kr/</t>
+  </si>
+  <si>
+    <t>https://sanhak-erp.kongju.ac.kr/</t>
+  </si>
+  <si>
+    <t>https://sanhak.inu.ac.kr/</t>
+  </si>
+  <si>
+    <t>https://sanhak-erp.kmou.ac.kr/</t>
+  </si>
+  <si>
+    <t>https://sanhakerp.deu.ac.kr/</t>
+  </si>
+  <si>
+    <t>https://iRCMS.inje.ac.kr/</t>
+  </si>
+  <si>
+    <t>https://shresch.hannam.ac.kr/</t>
+  </si>
+  <si>
+    <t>https://rnd.hsu.ac.kr/</t>
+  </si>
+  <si>
+    <t>https://sandan.kunsan.ac.kr/</t>
+  </si>
+  <si>
+    <t>https://uokiacf.kyungnam.ac.kr/</t>
+  </si>
+  <si>
+    <t>https://kitrnd.kumoh.ac.kr/</t>
+  </si>
+  <si>
+    <t>https://rnd.gnu.ac.kr/</t>
+  </si>
+  <si>
+    <t>https://gusanhak.gachon.ac.kr/</t>
+  </si>
+  <si>
+    <t>https://sanhak.mju.ac.kr/</t>
+  </si>
+  <si>
+    <t>https://sandanrnd.koreatech.ac.kr/</t>
+  </si>
+  <si>
+    <t>https://rnd.hallym.ac.kr/</t>
+  </si>
+  <si>
+    <t>https://r-erp.kau.ac.kr/</t>
+  </si>
+  <si>
+    <t>https://icf.konyang.ac.kr/</t>
+  </si>
+  <si>
+    <t>https://irms.cbnuh.or.kr/</t>
+  </si>
+  <si>
+    <t>https://kurnd.konkuk.ac.kr/</t>
+  </si>
+  <si>
+    <t>https://rnd.pknu.ac.kr/</t>
+  </si>
+  <si>
+    <t>https://sanhak-erp.pusan.ac.kr/</t>
+  </si>
+  <si>
+    <t>https://knu-icf.kangwon.ac.kr/</t>
+  </si>
+  <si>
+    <t>https://rerp.jnu.ac.kr/</t>
+  </si>
+  <si>
+    <t>https://rndbiz.cha.ac.kr/</t>
+  </si>
+  <si>
+    <t>https://iacf.sejong.ac.kr/</t>
+  </si>
+  <si>
+    <t>https://rndbiz.gilhospital.com/</t>
+  </si>
+  <si>
+    <t>https://rnd.cu.ac.kr/</t>
+  </si>
+  <si>
+    <t>https://rnd.dhu.ac.kr/</t>
+  </si>
+  <si>
+    <t>https://rnd.gknu.ac.kr/</t>
+  </si>
+  <si>
+    <t>https://rerp.hknu.ac.kr/</t>
+  </si>
+  <si>
+    <t>https://smrnd.sookmyung.ac.kr/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UNIV_CD</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SMARTRND_002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>한국방송통신대학교</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>한동대</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아주대학교의료원</t>
+  </si>
+  <si>
+    <t>교원대</t>
+  </si>
+  <si>
+    <t>https://sandan.knue.ac.kr/</t>
+  </si>
+  <si>
+    <t>SANRPM076</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SANRPM075</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SANRpm_proj76</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SMARTRND_022</t>
+  </si>
+  <si>
+    <t>Srnd_proj22</t>
+  </si>
+  <si>
+    <t>제주대</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>한국선급</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>경성대</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://kssanhak.ks.ac.kr/</t>
+  </si>
+  <si>
+    <t>대구대</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>경_성대학교</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://rnd.krs.co.kr/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://rnd.hufs.ac.kr/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://rnd.nsu.ac.kr/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://gtec.rndbiz.co.kr/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://cku.rndbiz.co.kr/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://sunmoon.rndbiz.co.kr/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://karts.rndbiz.co.kr/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://inhatc.rndbiz.co.kr/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://knou.rndbiz.co.kr/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://grms.rndbiz.co.kr/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://seowon.rndbiz.co.kr/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://gil.rndbiz.co.kr/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://cauhs.rndbiz.co.kr/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://yumc.rndbiz.co.kr/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://uhs.rndbiz.co.kr/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://chamc.rndbiz.co.kr/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://gjue.smartrnd.co.kr/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://sanhakpolice.smartrnd.co.kr/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://kdu.smartrnd.co.kr/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://kndu.smartrnd.co.kr/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://taejae.smartrnd.co.kr/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://dongduk.rndbiz.co.kr/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://sangji.rndbiz.co.kr/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://bc.rndbiz.co.kr/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://ds.rndbiz.co.kr/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://cukrnbf.smartrnd.co.kr/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://kduniv.smartrnd.co.kr/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://seoularts.smartrnd.co.kr/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://hscmt.smartrnd.co.kr/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://cs.smartrnd.co.kr/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://nambu.smartrnd.co.kr/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://kma.smartrnd.co.kr/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://hugs.smartrnd.co.kr/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://kings.smartrnd.co.kr/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://sunykorea.smartrnd.co.kr/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://kornu.smartrnd.co.kr/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://ubesanhak.smartrnd.co.kr/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://cpu.smartrnd.co.kr/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://hansei.smartrnd.co.kr/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://SKU.smartrnd.co.kr/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://kosin.smartrnd.co.kr/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://smit.smartrnd.co.kr/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://admin.rndbiz.co.kr/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://katri.rndbiz.co.kr/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://paik.rndbiz.co.kr/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://cup.rndbiz.co.kr/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://nmc.rndbiz.co.kr/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://kangnam.rndbiz.co.kr/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://syu.rndbiz.co.kr/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://dhu.rndbiz.co.kr/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://jwu.rndbiz.co.kr/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://sanproject.rndbiz.co.kr/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://ks.rndbiz.co.kr/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://kyungmin.rndbiz.co.kr/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://bu.rndbiz.co.kr/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://dhccf.rndbiz.co.kr/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://dongseo.rndbiz.co.kr/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://shinhan.rndbiz.co.kr/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://knuhbri.rndbiz.co.kr/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://dsmc.rndbiz.co.kr/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://anyang.rndbiz.co.kr/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://snue.rndbiz.co.kr/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://joongbu.rndbiz.co.kr/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://grisgwnu.rndbiz.co.kr/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://grisysu.rndbiz.co.kr/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://grisknu.rndbiz.co.kr/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://caughs.rndbiz.co.kr/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://swu.rndbiz.co.kr/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://ish.rndbiz.co.kr/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://kiu.rndbiz.co.kr/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://ywmc.rndbiz.co.kr/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://kbsmc.rndbiz.co.kr/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://jnuhcr.rndbiz.co.kr/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://gnuh.rndbiz.co.kr/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://tu.rndbiz.co.kr/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://damc.rndbiz.co.kr/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://nhimc.rndbiz.co.kr/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://hknu.rndbiz.co.kr/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://dsu.rndbiz.co.kr/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://pnuyh.rndbiz.co.kr/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://hs.rndbiz.co.kr/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://knuh.rndbiz.co.kr/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://nccgcsp-rndb.rndbiz.co.kr/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://kncaf.rndbiz.co.kr/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://induk.rndbiz.co.kr/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://dongyang.rndbiz.co.kr/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://kyuh.rndbiz.co.kr/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://handong.rndbiz.co.kr/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://knuheia.rndbiz.co.kr/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://daejin.rndbiz.co.kr/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://eumc.rndbiz.co.kr/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://wkuh.rndbiz.co.kr/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://gnuch.rndbiz.co.kr/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://pnuh.rndbiz.co.kr/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://hanseo.rndbiz.co.kr/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://cnuh.rndbiz.co.kr/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://ikw.rndbiz.co.kr/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://semyung.rndbiz.co.kr/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://mokwon.rndbiz.co.kr/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://cu.rndbiz.co.kr/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://skhu.rndbiz.co.kr/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://sanhak1.jejunu.ac.kr/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://rerp.handong.edu/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://hrms.aumc.ac.kr/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://r-erp.daegu.ac.kr/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://rerp.skuniv.ac.kr/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>순천향대</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://iacf.sch.ac.kr/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>한국전력국제원자력대학</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>국제뇌교육종합대학</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>국립암센터국제암대학</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KATRI시험연구원</t>
+  </si>
+  <si>
     <t>연세대학교원주세브란스기독병원</t>
   </si>
   <si>
-    <t>경일대학교</t>
-  </si>
-  <si>
-    <t>가톨릭관동대국제성모병원</t>
-  </si>
-  <si>
-    <t>서울여자대학교</t>
-  </si>
-  <si>
-    <t>중앙대학교광명병원</t>
-  </si>
-  <si>
-    <t>강원대학교 춘천캠퍼스</t>
-  </si>
-  <si>
-    <t>연세대학교 미래캠퍼스</t>
-  </si>
-  <si>
-    <t>강릉원주대학교</t>
-  </si>
-  <si>
-    <t>중부대학교</t>
-  </si>
-  <si>
-    <t>서울교육대학교</t>
-  </si>
-  <si>
-    <t>안양대학교</t>
-  </si>
-  <si>
-    <t>계명대학교 동산의료원</t>
-  </si>
-  <si>
-    <t>강원대학교병원</t>
-  </si>
-  <si>
-    <t>신한대학교</t>
-  </si>
-  <si>
-    <t>동서대학교</t>
-  </si>
-  <si>
-    <t>대구보건대학교</t>
-  </si>
-  <si>
-    <t>백석대학교</t>
-  </si>
-  <si>
-    <t>경민대학교</t>
-  </si>
-  <si>
-    <t>강남대학교</t>
-  </si>
-  <si>
-    <t>국립중앙의료원</t>
-  </si>
-  <si>
-    <t>부산가톨릭대학교</t>
-  </si>
-  <si>
-    <t>인제대학교 부산백병원</t>
-  </si>
-  <si>
-    <t>서울미디어대학원대학교</t>
-  </si>
-  <si>
-    <t>고신대학교</t>
-  </si>
-  <si>
-    <t>성결대학교</t>
-  </si>
-  <si>
-    <t>충북도립대학교</t>
-  </si>
-  <si>
-    <t>한세대학교</t>
-  </si>
-  <si>
-    <t>국제뇌교육종합대학원대학교</t>
-  </si>
-  <si>
-    <t>나사렛대학교</t>
-  </si>
-  <si>
-    <t>한국뉴육주립대학교</t>
-  </si>
-  <si>
-    <t>한국전력국제원자력대학원대학교</t>
-  </si>
-  <si>
-    <t>한림국제대학원대학교</t>
-  </si>
-  <si>
-    <t>육군사관학교</t>
-  </si>
-  <si>
-    <t>남부대학교</t>
-  </si>
-  <si>
-    <t>창신대학교</t>
-  </si>
-  <si>
-    <t>㈜에이치에스씨엠티</t>
-  </si>
-  <si>
-    <t>서울예술대학교</t>
-  </si>
-  <si>
-    <t>경동대학교</t>
-  </si>
-  <si>
-    <t>태재대학교</t>
-  </si>
-  <si>
-    <t>국방대학교</t>
-  </si>
-  <si>
-    <t>극동대학교</t>
-  </si>
-  <si>
-    <t>경찰대학교</t>
-  </si>
-  <si>
-    <t>SANRPM002</t>
-  </si>
-  <si>
-    <t>SANRPM003</t>
-  </si>
-  <si>
-    <t>SANRPM005</t>
-  </si>
-  <si>
-    <t>SANRPM006</t>
-  </si>
-  <si>
-    <t>SANRPM007</t>
-  </si>
-  <si>
-    <t>SANRPM008</t>
-  </si>
-  <si>
-    <t>SANRPM010</t>
-  </si>
-  <si>
-    <t>SANRPM011</t>
-  </si>
-  <si>
-    <t>SANRPM012</t>
-  </si>
-  <si>
-    <t>SANRPM016</t>
-  </si>
-  <si>
-    <t>SANRPM018</t>
-  </si>
-  <si>
-    <t>SANRPM019</t>
-  </si>
-  <si>
-    <t>SANRPM020</t>
-  </si>
-  <si>
-    <t>SANRPM021</t>
-  </si>
-  <si>
-    <t>SANRPM026</t>
-  </si>
-  <si>
-    <t>SANRPM029</t>
-  </si>
-  <si>
-    <t>SANRPM030</t>
-  </si>
-  <si>
-    <t>SANRPM036</t>
-  </si>
-  <si>
-    <t>SANRPM037</t>
-  </si>
-  <si>
-    <t>SANRPM038</t>
-  </si>
-  <si>
-    <t>SANRPM047</t>
-  </si>
-  <si>
-    <t>SANRPM048</t>
-  </si>
-  <si>
-    <t>SANRPM049</t>
-  </si>
-  <si>
-    <t>SANRPM050</t>
-  </si>
-  <si>
-    <t>SANRPM052</t>
-  </si>
-  <si>
-    <t>SANRPM054</t>
-  </si>
-  <si>
-    <t>SANRPM055</t>
-  </si>
-  <si>
-    <t>SANRPM057</t>
-  </si>
-  <si>
-    <t>SANRPM058</t>
-  </si>
-  <si>
-    <t>SANRPM062</t>
-  </si>
-  <si>
-    <t>SANRPM065</t>
-  </si>
-  <si>
-    <t>SMARTRND_008</t>
-  </si>
-  <si>
-    <t>SMARTRND_010</t>
-  </si>
-  <si>
-    <t>SMARTRND_012</t>
-  </si>
-  <si>
-    <t>SMARTRND_015</t>
-  </si>
-  <si>
-    <t>SANRPM009</t>
-  </si>
-  <si>
-    <t>SANRPM014</t>
-  </si>
-  <si>
-    <t>SANRPM015</t>
-  </si>
-  <si>
-    <t>SANRPM017</t>
-  </si>
-  <si>
-    <t>SANRPM013</t>
-  </si>
-  <si>
-    <t>SANRPM022</t>
-  </si>
-  <si>
-    <t>SANRPM023</t>
-  </si>
-  <si>
-    <t>SANRPM024</t>
-  </si>
-  <si>
-    <t>SANRPM025</t>
-  </si>
-  <si>
-    <t>SANRPM027</t>
-  </si>
-  <si>
-    <t>SANRPM028</t>
-  </si>
-  <si>
-    <t>SANRPM031</t>
-  </si>
-  <si>
-    <t>SANRPM032</t>
-  </si>
-  <si>
-    <t>SANRPM034</t>
-  </si>
-  <si>
-    <t>SANRPM035</t>
-  </si>
-  <si>
-    <t>SANRPM039</t>
-  </si>
-  <si>
-    <t>SANRPM040</t>
-  </si>
-  <si>
-    <t>SANRPM041</t>
-  </si>
-  <si>
-    <t>SANRPM042</t>
-  </si>
-  <si>
-    <t>SANRPM043</t>
-  </si>
-  <si>
-    <t>SANRPM044</t>
-  </si>
-  <si>
-    <t>SANRPM045</t>
-  </si>
-  <si>
-    <t>SANRPM046</t>
-  </si>
-  <si>
-    <t>SANRPM051</t>
-  </si>
-  <si>
-    <t>SANRPM053</t>
-  </si>
-  <si>
-    <t>SANRPM056</t>
-  </si>
-  <si>
-    <t>SANRPM059</t>
-  </si>
-  <si>
-    <t>SANRPM060</t>
-  </si>
-  <si>
-    <t>SANRPM061</t>
-  </si>
-  <si>
-    <t>SANRPM063</t>
-  </si>
-  <si>
-    <t>SANRPM064</t>
-  </si>
-  <si>
-    <t>SANRPM066</t>
-  </si>
-  <si>
-    <t>SANRPM067</t>
-  </si>
-  <si>
-    <t>SANRPM068</t>
-  </si>
-  <si>
-    <t>SANRPM069</t>
-  </si>
-  <si>
-    <t>SANRPM070</t>
-  </si>
-  <si>
-    <t>SANRPM071</t>
-  </si>
-  <si>
-    <t>SANRPM072</t>
-  </si>
-  <si>
-    <t>SANRPM073</t>
-  </si>
-  <si>
-    <t>SANRPM074</t>
-  </si>
-  <si>
-    <t>SANRPM_ADMIN</t>
-  </si>
-  <si>
-    <t>SMARTRND</t>
-  </si>
-  <si>
-    <t>SMARTRND_001</t>
-  </si>
-  <si>
-    <t>SMARTRND_003</t>
-  </si>
-  <si>
-    <t>SMARTRND_004</t>
-  </si>
-  <si>
-    <t>SMARTRND_005</t>
-  </si>
-  <si>
-    <t>SMARTRND_006</t>
-  </si>
-  <si>
-    <t>SMARTRND_009</t>
-  </si>
-  <si>
-    <t>SMARTRND_011</t>
-  </si>
-  <si>
-    <t>SMARTRND_013</t>
-  </si>
-  <si>
-    <t>SMARTRND_014</t>
-  </si>
-  <si>
-    <t>SMARTRND_016</t>
-  </si>
-  <si>
-    <t>SMARTRND_017</t>
-  </si>
-  <si>
-    <t>SMARTRND_018</t>
-  </si>
-  <si>
-    <t>SMARTRND_019</t>
-  </si>
-  <si>
-    <t>SMARTRND_020</t>
-  </si>
-  <si>
-    <t>SMARTRND_021</t>
-  </si>
-  <si>
-    <t>SANRpm_proj2</t>
-  </si>
-  <si>
-    <t>SANRpm_proj3</t>
-  </si>
-  <si>
-    <t>SANRpm_proj5</t>
-  </si>
-  <si>
-    <t>SANRpm_proj6</t>
-  </si>
-  <si>
-    <t>SANRpm_proj7</t>
-  </si>
-  <si>
-    <t>SANRpm_proj8</t>
-  </si>
-  <si>
-    <t>SANRpm_proj10</t>
-  </si>
-  <si>
-    <t>SANRpm_proj11</t>
-  </si>
-  <si>
-    <t>SANRpm_proj12</t>
-  </si>
-  <si>
-    <t>SANRpm_proj16</t>
-  </si>
-  <si>
-    <t>SANRpm_proj17</t>
-  </si>
-  <si>
-    <t>SANRpm_proj25</t>
-  </si>
-  <si>
-    <t>SANRpm_proj26</t>
-  </si>
-  <si>
-    <t>SANRpm_proj36</t>
-  </si>
-  <si>
-    <t>SANRpm_proj37</t>
-  </si>
-  <si>
-    <t>SANRpm_proj38</t>
-  </si>
-  <si>
-    <t>SANRpm_proj42</t>
-  </si>
-  <si>
-    <t>SANRpm_proj47</t>
-  </si>
-  <si>
-    <t>SANRpm_proj48</t>
-  </si>
-  <si>
-    <t>SANRpm_proj49</t>
-  </si>
-  <si>
-    <t>SANRpm_proj50</t>
-  </si>
-  <si>
-    <t>SANRpm_proj52</t>
-  </si>
-  <si>
-    <t>SANRpm_proj53</t>
-  </si>
-  <si>
-    <t>SANRpm_proj54</t>
-  </si>
-  <si>
-    <t>SANRpm_proj55</t>
-  </si>
-  <si>
-    <t>SANRpm_proj56</t>
-  </si>
-  <si>
-    <t>SANRpm_proj57</t>
-  </si>
-  <si>
-    <t>SANRpm_proj58</t>
-  </si>
-  <si>
-    <t>SANRpm_proj62</t>
-  </si>
-  <si>
-    <t>SANRpm_proj63</t>
-  </si>
-  <si>
-    <t>SANRpm_proj64</t>
-  </si>
-  <si>
-    <t>SANRpm_proj65</t>
-  </si>
-  <si>
-    <t>Srnd_proj8</t>
-  </si>
-  <si>
-    <t>Srnd_proj9</t>
-  </si>
-  <si>
-    <t>Srnd_proj10</t>
-  </si>
-  <si>
-    <t>Srnd_proj12</t>
-  </si>
-  <si>
-    <t>Srnd_proj15</t>
-  </si>
-  <si>
-    <t>SANRpm_proj9</t>
-  </si>
-  <si>
-    <t>SANRpm_proj14</t>
-  </si>
-  <si>
-    <t>SANRpm_proj15</t>
-  </si>
-  <si>
-    <t>SANRpm_proj18</t>
-  </si>
-  <si>
-    <t>SANRpm_proj19</t>
-  </si>
-  <si>
-    <t>SANRpm_proj20</t>
-  </si>
-  <si>
-    <t>SANRpm_proj21</t>
-  </si>
-  <si>
-    <t>SANRpm_proj13</t>
-  </si>
-  <si>
-    <t>SANRpm_Admin</t>
-  </si>
-  <si>
-    <t>SANRpm_proj22</t>
-  </si>
-  <si>
-    <t>SANRpm_proj23</t>
-  </si>
-  <si>
-    <t>SANRpm_proj24</t>
-  </si>
-  <si>
-    <t>SANRpm_proj27</t>
-  </si>
-  <si>
-    <t>SANRpm_proj28</t>
-  </si>
-  <si>
-    <t>SANRpm_proj29</t>
-  </si>
-  <si>
-    <t>SANRpm_proj30</t>
-  </si>
-  <si>
-    <t>SANRpm_proj31</t>
-  </si>
-  <si>
-    <t>SANRpm_proj32</t>
-  </si>
-  <si>
-    <t>SANRpm_proj34</t>
-  </si>
-  <si>
-    <t>SANRpm_proj35</t>
-  </si>
-  <si>
-    <t>SANRpm_proj39</t>
-  </si>
-  <si>
-    <t>SANRpm_proj40</t>
-  </si>
-  <si>
-    <t>SANRpm_proj41</t>
-  </si>
-  <si>
-    <t>SANRpm_proj43</t>
-  </si>
-  <si>
-    <t>SANRpm_proj44</t>
-  </si>
-  <si>
-    <t>SANRpm_proj45</t>
-  </si>
-  <si>
-    <t>SANRpm_proj46</t>
-  </si>
-  <si>
-    <t>SANRpm_proj51</t>
-  </si>
-  <si>
-    <t>SANRpm_proj59</t>
-  </si>
-  <si>
-    <t>SANRpm_proj60</t>
-  </si>
-  <si>
-    <t>SANRpm_proj61</t>
-  </si>
-  <si>
-    <t>SANRpm_proj66</t>
-  </si>
-  <si>
-    <t>SANRpm_proj67</t>
-  </si>
-  <si>
-    <t>SANRpm_proj68</t>
-  </si>
-  <si>
-    <t>SANRpm_proj69</t>
-  </si>
-  <si>
-    <t>SANRpm_proj70</t>
-  </si>
-  <si>
-    <t>SANRpm_proj71</t>
-  </si>
-  <si>
-    <t>SANRpm_proj72</t>
-  </si>
-  <si>
-    <t>SANRpm_proj73</t>
-  </si>
-  <si>
-    <t>SANRpm_proj74</t>
-  </si>
-  <si>
-    <t>SANRpm_proj75</t>
-  </si>
-  <si>
-    <t>Srnd_project</t>
-  </si>
-  <si>
-    <t>Srnd_proj1</t>
-  </si>
-  <si>
-    <t>Srnd_proj2</t>
-  </si>
-  <si>
-    <t>Srnd_proj3</t>
-  </si>
-  <si>
-    <t>Srnd_proj4</t>
-  </si>
-  <si>
-    <t>Srnd_proj5</t>
-  </si>
-  <si>
-    <t>Srnd_proj6</t>
-  </si>
-  <si>
-    <t>Srnd_proj11</t>
-  </si>
-  <si>
-    <t>Srnd_proj13</t>
-  </si>
-  <si>
-    <t>Srnd_proj14</t>
-  </si>
-  <si>
-    <t>Srnd_proj16</t>
-  </si>
-  <si>
-    <t>Srnd_proj17</t>
-  </si>
-  <si>
-    <t>Srnd_proj18</t>
-  </si>
-  <si>
-    <t>Srnd_proj19</t>
-  </si>
-  <si>
-    <t>Srnd_proj20</t>
-  </si>
-  <si>
-    <t>Srnd_proj21</t>
-  </si>
-  <si>
-    <t>홍익대</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>교통대</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>한밭대</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>충남대</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>공주대</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>인천대</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>해양대</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>동의대</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>인제대</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>한남대</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>호서대</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>군산대</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>경남대</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>금오공대</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>경상대</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>가천대</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>명지대</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>한기대</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>한림대</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>항공대</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>건양대</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>충북대병원</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>건국대</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>부경대</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>부산대</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>강원대</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>전남대</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>남서울대</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>서경대</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>차의과대</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>세종대</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>대구가톨릭대</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>국립경국대</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>한국외대</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>한경대</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>숙명여대</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>기관명</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DB</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>WAS</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>구분</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>URL</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SERVER2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SERVER1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SaaS</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Standard</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>구분</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>기관명</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>URL</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://sanhak.hongik.ac.kr/</t>
-  </si>
-  <si>
-    <t>https://sanhak-erp.ut.ac.kr/</t>
-  </si>
-  <si>
-    <t>https://rnd.hanbat.ac.kr/</t>
-  </si>
-  <si>
-    <t>https://forb.cnu.ac.kr/</t>
-  </si>
-  <si>
-    <t>https://sanhak-erp.kongju.ac.kr/</t>
-  </si>
-  <si>
-    <t>https://sanhak.inu.ac.kr/</t>
-  </si>
-  <si>
-    <t>https://sanhak-erp.kmou.ac.kr/</t>
-  </si>
-  <si>
-    <t>https://sanhakerp.deu.ac.kr/</t>
-  </si>
-  <si>
-    <t>https://iRCMS.inje.ac.kr/</t>
-  </si>
-  <si>
-    <t>https://shresch.hannam.ac.kr/</t>
-  </si>
-  <si>
-    <t>https://rnd.hsu.ac.kr/</t>
-  </si>
-  <si>
-    <t>https://sandan.kunsan.ac.kr/</t>
-  </si>
-  <si>
-    <t>https://uokiacf.kyungnam.ac.kr/</t>
-  </si>
-  <si>
-    <t>https://kitrnd.kumoh.ac.kr/</t>
-  </si>
-  <si>
-    <t>https://rnd.gnu.ac.kr/</t>
-  </si>
-  <si>
-    <t>https://gusanhak.gachon.ac.kr/</t>
-  </si>
-  <si>
-    <t>https://sanhak.mju.ac.kr/</t>
-  </si>
-  <si>
-    <t>https://sandanrnd.koreatech.ac.kr/</t>
-  </si>
-  <si>
-    <t>https://rnd.hallym.ac.kr/</t>
-  </si>
-  <si>
-    <t>https://r-erp.kau.ac.kr/</t>
-  </si>
-  <si>
-    <t>https://icf.konyang.ac.kr/</t>
-  </si>
-  <si>
-    <t>https://irms.cbnuh.or.kr/</t>
-  </si>
-  <si>
-    <t>https://kurnd.konkuk.ac.kr/</t>
-  </si>
-  <si>
-    <t>https://rnd.pknu.ac.kr/</t>
-  </si>
-  <si>
-    <t>https://sanhak-erp.pusan.ac.kr/</t>
-  </si>
-  <si>
-    <t>https://knu-icf.kangwon.ac.kr/</t>
-  </si>
-  <si>
-    <t>https://rerp.jnu.ac.kr/</t>
-  </si>
-  <si>
-    <t>https://rndbiz.cha.ac.kr/</t>
-  </si>
-  <si>
-    <t>https://iacf.sejong.ac.kr/</t>
-  </si>
-  <si>
-    <t>https://rndbiz.gilhospital.com/</t>
-  </si>
-  <si>
-    <t>https://rnd.cu.ac.kr/</t>
-  </si>
-  <si>
-    <t>https://rnd.dhu.ac.kr/</t>
-  </si>
-  <si>
-    <t>https://rnd.gknu.ac.kr/</t>
-  </si>
-  <si>
-    <t>https://rerp.hknu.ac.kr/</t>
-  </si>
-  <si>
-    <t>https://smrnd.sookmyung.ac.kr/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>UNIV_CD</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SMARTRND_002</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>한국방송통신대학교</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>`</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>한동대</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>아주대학교의료원</t>
-  </si>
-  <si>
-    <t>교원대</t>
-  </si>
-  <si>
-    <t>https://sandan.knue.ac.kr/</t>
-  </si>
-  <si>
-    <t>KATRI시험연구원</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SANRPM076</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SANRPM075</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SANRpm_proj76</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>공주교육대</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SMARTRND_022</t>
-  </si>
-  <si>
-    <t>Srnd_proj22</t>
-  </si>
-  <si>
-    <t>제주대</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>한국선급</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>경성대</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://kssanhak.ks.ac.kr/</t>
-  </si>
-  <si>
-    <t>대구대</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>경_성대학교</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://rnd.krs.co.kr/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://rnd.hufs.ac.kr/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://rnd.nsu.ac.kr/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://gtec.rndbiz.co.kr/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://cku.rndbiz.co.kr/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://sunmoon.rndbiz.co.kr/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://karts.rndbiz.co.kr/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://inhatc.rndbiz.co.kr/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://knou.rndbiz.co.kr/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://grms.rndbiz.co.kr/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://seowon.rndbiz.co.kr/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://gil.rndbiz.co.kr/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://cauhs.rndbiz.co.kr/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://yumc.rndbiz.co.kr/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://uhs.rndbiz.co.kr/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://chamc.rndbiz.co.kr/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://gjue.smartrnd.co.kr/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://sanhakpolice.smartrnd.co.kr/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://kdu.smartrnd.co.kr/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://kndu.smartrnd.co.kr/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://taejae.smartrnd.co.kr/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://dongduk.rndbiz.co.kr/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://sangji.rndbiz.co.kr/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://bc.rndbiz.co.kr/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://ds.rndbiz.co.kr/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://cukrnbf.smartrnd.co.kr/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://kduniv.smartrnd.co.kr/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://seoularts.smartrnd.co.kr/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://hscmt.smartrnd.co.kr/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://cs.smartrnd.co.kr/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://nambu.smartrnd.co.kr/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://kma.smartrnd.co.kr/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://hugs.smartrnd.co.kr/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://kings.smartrnd.co.kr/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://sunykorea.smartrnd.co.kr/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://kornu.smartrnd.co.kr/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://ubesanhak.smartrnd.co.kr/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://cpu.smartrnd.co.kr/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://hansei.smartrnd.co.kr/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://SKU.smartrnd.co.kr/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://kosin.smartrnd.co.kr/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://smit.smartrnd.co.kr/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://admin.rndbiz.co.kr/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://katri.rndbiz.co.kr/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://paik.rndbiz.co.kr/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://cup.rndbiz.co.kr/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://nmc.rndbiz.co.kr/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://kangnam.rndbiz.co.kr/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://syu.rndbiz.co.kr/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://dhu.rndbiz.co.kr/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://jwu.rndbiz.co.kr/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://sanproject.rndbiz.co.kr/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://ks.rndbiz.co.kr/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://kyungmin.rndbiz.co.kr/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://bu.rndbiz.co.kr/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://dhccf.rndbiz.co.kr/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://dongseo.rndbiz.co.kr/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://shinhan.rndbiz.co.kr/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://knuhbri.rndbiz.co.kr/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://dsmc.rndbiz.co.kr/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://anyang.rndbiz.co.kr/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://snue.rndbiz.co.kr/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://joongbu.rndbiz.co.kr/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://grisgwnu.rndbiz.co.kr/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://grisysu.rndbiz.co.kr/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://grisknu.rndbiz.co.kr/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://caughs.rndbiz.co.kr/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://swu.rndbiz.co.kr/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://ish.rndbiz.co.kr/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://kiu.rndbiz.co.kr/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://ywmc.rndbiz.co.kr/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://kbsmc.rndbiz.co.kr/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://jnuhcr.rndbiz.co.kr/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://gnuh.rndbiz.co.kr/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://tu.rndbiz.co.kr/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://damc.rndbiz.co.kr/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://nhimc.rndbiz.co.kr/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://hknu.rndbiz.co.kr/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://dsu.rndbiz.co.kr/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://pnuyh.rndbiz.co.kr/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://hs.rndbiz.co.kr/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://knuh.rndbiz.co.kr/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://nccgcsp-rndb.rndbiz.co.kr/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://kncaf.rndbiz.co.kr/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://induk.rndbiz.co.kr/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://dongyang.rndbiz.co.kr/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://kyuh.rndbiz.co.kr/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://handong.rndbiz.co.kr/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://knuheia.rndbiz.co.kr/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://daejin.rndbiz.co.kr/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://eumc.rndbiz.co.kr/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://wkuh.rndbiz.co.kr/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://gnuch.rndbiz.co.kr/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://pnuh.rndbiz.co.kr/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://hanseo.rndbiz.co.kr/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://cnuh.rndbiz.co.kr/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://ikw.rndbiz.co.kr/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://semyung.rndbiz.co.kr/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://mokwon.rndbiz.co.kr/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://cu.rndbiz.co.kr/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>http://skhu.rndbiz.co.kr/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://sanhak1.jejunu.ac.kr/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://rerp.handong.edu/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://hrms.aumc.ac.kr/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://r-erp.daegu.ac.kr/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://rerp.skuniv.ac.kr/</t>
+    <t>공주교육대학교</t>
+  </si>
+  <si>
+    <t>초당대학교</t>
+  </si>
+  <si>
+    <t>한국체육대학교</t>
+  </si>
+  <si>
+    <t>용인대학교</t>
+  </si>
+  <si>
+    <t>SMARTRND_023</t>
+  </si>
+  <si>
+    <t>SMARTRND_024</t>
+  </si>
+  <si>
+    <t>SMARTRND_025</t>
+  </si>
+  <si>
+    <t>Srnd_proj23</t>
+  </si>
+  <si>
+    <t>Srnd_proj24</t>
+  </si>
+  <si>
+    <t>Srnd_proj25</t>
+  </si>
+  <si>
+    <t>http://rnd-cdu.smartrnd.co.kr</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://knsu.smartrnd.co.kr</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://yiu.smartrnd.co.kr</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>IP1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>IP2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10.190.2.38</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10.190.2.42</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>183.111.151.71</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10.190.2.46</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10.190.2.29</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10.190.2.32</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10.190.2.165</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10.190.2.166</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10.190.2.225</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10.190.2.226</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1718,7 +1810,13 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2002,460 +2100,460 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D46"/>
+  <dimension ref="A1:D47"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="B1" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="C1" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="D1" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="B2" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="C2">
         <v>11</v>
       </c>
       <c r="D2" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="B3" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="C3">
         <v>12</v>
       </c>
       <c r="D3" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="B4" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="C4">
         <v>13</v>
       </c>
       <c r="D4" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="B5" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="C5">
         <v>14</v>
       </c>
       <c r="D5" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="B6" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="C6">
         <v>15</v>
       </c>
       <c r="D6" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="B7" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="C7">
         <v>16</v>
       </c>
       <c r="D7" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="B8" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="C8">
         <v>17</v>
       </c>
       <c r="D8" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="B9" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="C9">
         <v>18</v>
       </c>
       <c r="D9" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="B10" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="C10">
         <v>19</v>
       </c>
       <c r="D10" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="B11" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="C11">
         <v>20</v>
       </c>
       <c r="D11" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="B12" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="C12">
         <v>21</v>
       </c>
       <c r="D12" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="B13" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="C13">
         <v>22</v>
       </c>
       <c r="D13" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="B14" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="C14">
         <v>23</v>
       </c>
       <c r="D14" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="B15" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="C15">
         <v>24</v>
       </c>
       <c r="D15" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="B16" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="C16">
         <v>25</v>
       </c>
       <c r="D16" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="B17" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="C17">
         <v>26</v>
       </c>
       <c r="D17" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="B18" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="C18">
         <v>27</v>
       </c>
       <c r="D18" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="B19" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="C19">
         <v>28</v>
       </c>
       <c r="D19" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="B20" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="C20">
         <v>29</v>
       </c>
       <c r="D20" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="B21" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="C21">
         <v>30</v>
       </c>
       <c r="D21" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="B22" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="C22">
         <v>31</v>
       </c>
       <c r="D22" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="B23" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C23">
         <v>32</v>
       </c>
       <c r="D23" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="B24" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="C24">
         <v>33</v>
       </c>
       <c r="D24" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="B25" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="C25">
         <v>34</v>
       </c>
       <c r="D25" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="B26" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="C26">
         <v>35</v>
       </c>
       <c r="D26" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="B27" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="C27">
         <v>36</v>
       </c>
       <c r="D27" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="B28" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="C28">
         <v>37</v>
       </c>
       <c r="D28" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="B29" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="C29">
         <v>38</v>
       </c>
       <c r="D29" t="s">
-        <v>388</v>
+        <v>381</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="B30" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="C30">
         <v>39</v>
       </c>
       <c r="D30" t="s">
-        <v>491</v>
+        <v>484</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="B31" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="C31">
         <v>40</v>
       </c>
       <c r="D31" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="B32" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="C32">
         <v>41</v>
       </c>
       <c r="D32" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="B33" t="s">
         <v>0</v>
@@ -2464,26 +2562,26 @@
         <v>42</v>
       </c>
       <c r="D33" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="B34" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="C34">
         <v>43</v>
       </c>
       <c r="D34" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="B35" t="s">
         <v>1</v>
@@ -2492,161 +2590,175 @@
         <v>44</v>
       </c>
       <c r="D35" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="B36" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="C36">
         <v>45</v>
       </c>
       <c r="D36" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="B37" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="C37">
         <v>46</v>
       </c>
       <c r="D37" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="B38" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="C38">
         <v>47</v>
       </c>
       <c r="D38" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="B39" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="C39">
         <v>48</v>
       </c>
       <c r="D39" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="B40" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="C40">
         <v>49</v>
       </c>
       <c r="D40" t="s">
-        <v>488</v>
+        <v>481</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="B41" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="C41">
         <v>50</v>
       </c>
       <c r="D41" t="s">
-        <v>489</v>
+        <v>482</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="B42" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="C42">
         <v>51</v>
       </c>
       <c r="D42" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="B43" t="s">
-        <v>380</v>
+        <v>373</v>
       </c>
       <c r="C43">
         <v>52</v>
       </c>
       <c r="D43" t="s">
-        <v>487</v>
+        <v>480</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="B44" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="C44">
         <v>53</v>
       </c>
       <c r="D44" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="B45" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="C45">
         <v>54</v>
       </c>
       <c r="D45" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="B46" t="s">
-        <v>384</v>
+        <v>377</v>
       </c>
       <c r="C46">
         <v>55</v>
       </c>
       <c r="D46" t="s">
-        <v>490</v>
+        <v>483</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>322</v>
+      </c>
+      <c r="B47" t="s">
+        <v>485</v>
+      </c>
+      <c r="C47">
+        <v>56</v>
+      </c>
+      <c r="D47" t="s">
+        <v>486</v>
       </c>
     </row>
   </sheetData>
@@ -2658,53 +2770,61 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G99"/>
+  <dimension ref="A1:I102"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="1" max="1" width="14.875" customWidth="1"/>
     <col min="2" max="2" width="31.75" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="16.75" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="32.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="10.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="B1" t="s">
+        <v>314</v>
+      </c>
+      <c r="C1" t="s">
+        <v>315</v>
+      </c>
+      <c r="D1" t="s">
+        <v>316</v>
+      </c>
+      <c r="E1" t="s">
         <v>318</v>
       </c>
-      <c r="C1" t="s">
+      <c r="F1" t="s">
+        <v>320</v>
+      </c>
+      <c r="G1" t="s">
         <v>319</v>
       </c>
-      <c r="D1" t="s">
-        <v>320</v>
-      </c>
-      <c r="E1" t="s">
-        <v>322</v>
-      </c>
-      <c r="F1" t="s">
-        <v>324</v>
-      </c>
-      <c r="G1" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H1" t="s">
+        <v>505</v>
+      </c>
+      <c r="I1" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B2" t="s">
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D2" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="E2" t="s">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="F2">
         <v>1</v>
@@ -2712,22 +2832,28 @@
       <c r="G2">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H2" t="s">
+        <v>507</v>
+      </c>
+      <c r="I2" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B3" t="s">
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D3" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="E3" t="s">
-        <v>390</v>
+        <v>383</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -2735,22 +2861,28 @@
       <c r="G3">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H3" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B4" t="s">
         <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D4" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="E4" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
       <c r="F4">
         <v>1</v>
@@ -2758,22 +2890,28 @@
       <c r="G4">
         <v>2</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H4" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B5" t="s">
         <v>7</v>
       </c>
       <c r="C5" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="D5" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="E5" t="s">
-        <v>392</v>
+        <v>385</v>
       </c>
       <c r="F5">
         <v>1</v>
@@ -2781,22 +2919,28 @@
       <c r="G5">
         <v>2</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H5" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B6" t="s">
         <v>8</v>
       </c>
       <c r="C6" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D6" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E6" t="s">
-        <v>393</v>
+        <v>386</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -2804,22 +2948,28 @@
       <c r="G6">
         <v>2</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H6" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B7" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="C7" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D7" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="E7" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="F7">
         <v>1</v>
@@ -2827,22 +2977,28 @@
       <c r="G7">
         <v>2</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H7" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B8" t="s">
         <v>9</v>
       </c>
       <c r="C8" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="D8" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="E8" t="s">
-        <v>395</v>
+        <v>388</v>
       </c>
       <c r="F8">
         <v>1</v>
@@ -2850,22 +3006,28 @@
       <c r="G8">
         <v>2</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H8" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B9" t="s">
         <v>10</v>
       </c>
       <c r="C9" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="D9" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="E9" t="s">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="F9">
         <v>1</v>
@@ -2873,22 +3035,28 @@
       <c r="G9">
         <v>2</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H9" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B10" t="s">
         <v>11</v>
       </c>
       <c r="C10" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D10" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="E10" t="s">
-        <v>397</v>
+        <v>390</v>
       </c>
       <c r="F10">
         <v>1</v>
@@ -2896,22 +3064,28 @@
       <c r="G10">
         <v>2</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H10" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B11" t="s">
         <v>12</v>
       </c>
       <c r="C11" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D11" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="E11" t="s">
-        <v>398</v>
+        <v>391</v>
       </c>
       <c r="F11">
         <v>1</v>
@@ -2919,22 +3093,28 @@
       <c r="G11">
         <v>2</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H11" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B12" t="s">
         <v>13</v>
       </c>
       <c r="C12" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="D12" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="E12" t="s">
-        <v>400</v>
+        <v>393</v>
       </c>
       <c r="F12">
         <v>1</v>
@@ -2942,22 +3122,28 @@
       <c r="G12">
         <v>2</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H12" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B13" t="s">
         <v>14</v>
       </c>
       <c r="C13" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="D13" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="E13" t="s">
-        <v>399</v>
+        <v>392</v>
       </c>
       <c r="F13">
         <v>1</v>
@@ -2965,22 +3151,28 @@
       <c r="G13">
         <v>2</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H13" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B14" t="s">
         <v>15</v>
       </c>
       <c r="C14" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D14" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="E14" t="s">
-        <v>401</v>
+        <v>394</v>
       </c>
       <c r="F14">
         <v>1</v>
@@ -2988,22 +3180,28 @@
       <c r="G14">
         <v>2</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H14" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B15" t="s">
         <v>16</v>
       </c>
       <c r="C15" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D15" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="E15" t="s">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="F15">
         <v>1</v>
@@ -3011,22 +3209,28 @@
       <c r="G15">
         <v>2</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H15" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B16" t="s">
         <v>17</v>
       </c>
       <c r="C16" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D16" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="E16" t="s">
-        <v>408</v>
+        <v>401</v>
       </c>
       <c r="F16">
         <v>1</v>
@@ -3034,22 +3238,28 @@
       <c r="G16">
         <v>2</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H16" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B17" t="s">
         <v>18</v>
       </c>
       <c r="C17" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D17" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="E17" t="s">
-        <v>409</v>
+        <v>402</v>
       </c>
       <c r="F17">
         <v>1</v>
@@ -3057,22 +3267,28 @@
       <c r="G17">
         <v>2</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H17" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B18" t="s">
         <v>19</v>
       </c>
       <c r="C18" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D18" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="E18" t="s">
-        <v>410</v>
+        <v>403</v>
       </c>
       <c r="F18">
         <v>1</v>
@@ -3080,22 +3296,28 @@
       <c r="G18">
         <v>2</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H18" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B19" t="s">
         <v>20</v>
       </c>
       <c r="C19" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D19" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="E19" t="s">
-        <v>434</v>
+        <v>427</v>
       </c>
       <c r="F19">
         <v>1</v>
@@ -3103,22 +3325,28 @@
       <c r="G19">
         <v>2</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H19" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B20" t="s">
         <v>21</v>
       </c>
       <c r="C20" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="D20" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="E20" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="F20">
         <v>1</v>
@@ -3126,22 +3354,28 @@
       <c r="G20">
         <v>2</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H20" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B21" t="s">
         <v>22</v>
       </c>
       <c r="C21" t="s">
-        <v>368</v>
+        <v>131</v>
       </c>
       <c r="D21" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="E21" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="F21">
         <v>1</v>
@@ -3149,22 +3383,28 @@
       <c r="G21">
         <v>2</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H21" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B22" t="s">
         <v>23</v>
       </c>
       <c r="C22" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="D22" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="E22" t="s">
-        <v>437</v>
+        <v>430</v>
       </c>
       <c r="F22">
         <v>1</v>
@@ -3172,22 +3412,28 @@
       <c r="G22">
         <v>2</v>
       </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H22" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B23" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="C23" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D23" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="E23" t="s">
-        <v>438</v>
+        <v>431</v>
       </c>
       <c r="F23">
         <v>3</v>
@@ -3195,22 +3441,28 @@
       <c r="G23">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H23" t="s">
+        <v>509</v>
+      </c>
+      <c r="I23" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B24" t="s">
         <v>25</v>
       </c>
       <c r="C24" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="D24" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="E24" t="s">
-        <v>486</v>
+        <v>479</v>
       </c>
       <c r="F24">
         <v>3</v>
@@ -3218,22 +3470,28 @@
       <c r="G24">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H24" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B25" t="s">
         <v>26</v>
       </c>
       <c r="C25" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="D25" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="E25" t="s">
-        <v>485</v>
+        <v>478</v>
       </c>
       <c r="F25">
         <v>3</v>
@@ -3241,22 +3499,28 @@
       <c r="G25">
         <v>4</v>
       </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H25" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B26" t="s">
         <v>27</v>
       </c>
       <c r="C26" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="D26" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="E26" t="s">
-        <v>484</v>
+        <v>477</v>
       </c>
       <c r="F26">
         <v>3</v>
@@ -3264,22 +3528,28 @@
       <c r="G26">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H26" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B27" t="s">
         <v>28</v>
       </c>
       <c r="C27" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D27" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="E27" t="s">
-        <v>483</v>
+        <v>476</v>
       </c>
       <c r="F27">
         <v>3</v>
@@ -3287,22 +3557,28 @@
       <c r="G27">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H27" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B28" t="s">
         <v>29</v>
       </c>
       <c r="C28" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D28" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="E28" t="s">
-        <v>482</v>
+        <v>475</v>
       </c>
       <c r="F28">
         <v>3</v>
@@ -3310,22 +3586,28 @@
       <c r="G28">
         <v>4</v>
       </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H28" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B29" t="s">
         <v>30</v>
       </c>
       <c r="C29" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="D29" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="E29" t="s">
-        <v>481</v>
+        <v>474</v>
       </c>
       <c r="F29">
         <v>3</v>
@@ -3333,22 +3615,28 @@
       <c r="G29">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H29" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B30" t="s">
         <v>31</v>
       </c>
       <c r="C30" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="D30" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="E30" t="s">
-        <v>480</v>
+        <v>473</v>
       </c>
       <c r="F30">
         <v>3</v>
@@ -3356,22 +3644,28 @@
       <c r="G30">
         <v>4</v>
       </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H30" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B31" t="s">
         <v>32</v>
       </c>
       <c r="C31" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="D31" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="E31" t="s">
-        <v>479</v>
+        <v>472</v>
       </c>
       <c r="F31">
         <v>3</v>
@@ -3379,22 +3673,28 @@
       <c r="G31">
         <v>4</v>
       </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H31" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B32" t="s">
         <v>33</v>
       </c>
       <c r="C32" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="D32" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="E32" t="s">
-        <v>478</v>
+        <v>471</v>
       </c>
       <c r="F32">
         <v>3</v>
@@ -3402,22 +3702,28 @@
       <c r="G32">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H32" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="I32" s="2" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B33" t="s">
         <v>34</v>
       </c>
       <c r="C33" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="D33" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="E33" t="s">
-        <v>477</v>
+        <v>470</v>
       </c>
       <c r="F33">
         <v>3</v>
@@ -3425,22 +3731,28 @@
       <c r="G33">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H33" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="I33" s="2" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B34" t="s">
         <v>35</v>
       </c>
       <c r="C34" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D34" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="E34" t="s">
-        <v>476</v>
+        <v>469</v>
       </c>
       <c r="F34">
         <v>3</v>
@@ -3448,22 +3760,28 @@
       <c r="G34">
         <v>4</v>
       </c>
-    </row>
-    <row r="35" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H34" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="I34" s="2" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B35" t="s">
         <v>36</v>
       </c>
       <c r="C35" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="D35" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="E35" t="s">
-        <v>475</v>
+        <v>468</v>
       </c>
       <c r="F35">
         <v>3</v>
@@ -3471,22 +3789,28 @@
       <c r="G35">
         <v>4</v>
       </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H35" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="I35" s="2" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B36" t="s">
         <v>37</v>
       </c>
       <c r="C36" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="D36" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="E36" t="s">
-        <v>474</v>
+        <v>467</v>
       </c>
       <c r="F36">
         <v>3</v>
@@ -3494,22 +3818,28 @@
       <c r="G36">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H36" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="I36" s="2" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B37" t="s">
         <v>38</v>
       </c>
       <c r="C37" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D37" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="E37" t="s">
-        <v>473</v>
+        <v>466</v>
       </c>
       <c r="F37">
         <v>3</v>
@@ -3517,22 +3847,28 @@
       <c r="G37">
         <v>4</v>
       </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H37" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="I37" s="2" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B38" t="s">
         <v>39</v>
       </c>
       <c r="C38" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D38" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="E38" t="s">
-        <v>472</v>
+        <v>465</v>
       </c>
       <c r="F38">
         <v>3</v>
@@ -3540,22 +3876,28 @@
       <c r="G38">
         <v>4</v>
       </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H38" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="I38" s="2" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B39" t="s">
         <v>40</v>
       </c>
       <c r="C39" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="D39" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="E39" t="s">
-        <v>471</v>
+        <v>464</v>
       </c>
       <c r="F39">
         <v>3</v>
@@ -3563,22 +3905,28 @@
       <c r="G39">
         <v>4</v>
       </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H39" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="I39" s="2" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B40" t="s">
         <v>41</v>
       </c>
       <c r="C40" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="D40" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="E40" t="s">
-        <v>470</v>
+        <v>463</v>
       </c>
       <c r="F40">
         <v>3</v>
@@ -3586,22 +3934,28 @@
       <c r="G40">
         <v>4</v>
       </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H40" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="I40" s="2" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B41" t="s">
         <v>42</v>
       </c>
       <c r="C41" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="D41" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="E41" t="s">
-        <v>469</v>
+        <v>462</v>
       </c>
       <c r="F41">
         <v>3</v>
@@ -3609,22 +3963,28 @@
       <c r="G41">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H41" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="I41" s="2" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B42" t="s">
-        <v>43</v>
+        <v>489</v>
       </c>
       <c r="C42" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="D42" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="E42" t="s">
-        <v>468</v>
+        <v>461</v>
       </c>
       <c r="F42">
         <v>3</v>
@@ -3632,22 +3992,28 @@
       <c r="G42">
         <v>4</v>
       </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H42" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="I42" s="2" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B43" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C43" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="D43" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="E43" t="s">
-        <v>467</v>
+        <v>460</v>
       </c>
       <c r="F43">
         <v>3</v>
@@ -3655,22 +4021,28 @@
       <c r="G43">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H43" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="I43" s="2" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B44" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C44" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="D44" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="E44" t="s">
-        <v>466</v>
+        <v>459</v>
       </c>
       <c r="F44">
         <v>5</v>
@@ -3678,22 +4050,28 @@
       <c r="G44">
         <v>6</v>
       </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H44" t="s">
+        <v>511</v>
+      </c>
+      <c r="I44" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B45" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C45" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="D45" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="E45" t="s">
-        <v>465</v>
+        <v>458</v>
       </c>
       <c r="F45">
         <v>5</v>
@@ -3701,22 +4079,28 @@
       <c r="G45">
         <v>6</v>
       </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H45" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="I45" s="2" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B46" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C46" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="D46" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="E46" t="s">
-        <v>464</v>
+        <v>457</v>
       </c>
       <c r="F46">
         <v>5</v>
@@ -3724,22 +4108,28 @@
       <c r="G46">
         <v>6</v>
       </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H46" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="I46" s="2" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B47" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C47" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D47" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="E47" t="s">
-        <v>463</v>
+        <v>456</v>
       </c>
       <c r="F47">
         <v>5</v>
@@ -3747,22 +4137,28 @@
       <c r="G47">
         <v>6</v>
       </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H47" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="I47" s="2" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B48" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C48" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="D48" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="E48" t="s">
-        <v>462</v>
+        <v>455</v>
       </c>
       <c r="F48">
         <v>5</v>
@@ -3770,22 +4166,28 @@
       <c r="G48">
         <v>6</v>
       </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H48" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="I48" s="2" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B49" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C49" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="D49" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="E49" t="s">
-        <v>461</v>
+        <v>454</v>
       </c>
       <c r="F49">
         <v>5</v>
@@ -3793,22 +4195,28 @@
       <c r="G49">
         <v>6</v>
       </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H49" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="I49" s="2" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B50" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C50" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="D50" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="E50" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="F50">
         <v>5</v>
@@ -3816,22 +4224,28 @@
       <c r="G50">
         <v>6</v>
       </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H50" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="I50" s="2" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B51" t="s">
         <v>2</v>
       </c>
       <c r="C51" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="D51" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="E51" t="s">
-        <v>459</v>
+        <v>452</v>
       </c>
       <c r="F51">
         <v>5</v>
@@ -3839,22 +4253,28 @@
       <c r="G51">
         <v>6</v>
       </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H51" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="I51" s="2" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B52" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C52" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="D52" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="E52" t="s">
-        <v>458</v>
+        <v>451</v>
       </c>
       <c r="F52">
         <v>5</v>
@@ -3862,22 +4282,28 @@
       <c r="G52">
         <v>6</v>
       </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H52" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="I52" s="2" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B53" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C53" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="D53" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="E53" t="s">
-        <v>457</v>
+        <v>450</v>
       </c>
       <c r="F53">
         <v>5</v>
@@ -3885,22 +4311,28 @@
       <c r="G53">
         <v>6</v>
       </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H53" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="I53" s="2" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B54" t="s">
-        <v>54</v>
+        <v>491</v>
       </c>
       <c r="C54" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D54" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="E54" t="s">
-        <v>456</v>
+        <v>449</v>
       </c>
       <c r="F54">
         <v>5</v>
@@ -3908,22 +4340,28 @@
       <c r="G54">
         <v>6</v>
       </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H54" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="I54" s="2" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B55" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C55" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="D55" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="E55" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="F55">
         <v>5</v>
@@ -3931,22 +4369,28 @@
       <c r="G55">
         <v>6</v>
       </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H55" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="I55" s="2" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B56" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C56" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="D56" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="E56" t="s">
-        <v>454</v>
+        <v>447</v>
       </c>
       <c r="F56">
         <v>5</v>
@@ -3954,22 +4398,28 @@
       <c r="G56">
         <v>6</v>
       </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H56" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="I56" s="2" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B57" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C57" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="D57" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="E57" t="s">
-        <v>453</v>
+        <v>446</v>
       </c>
       <c r="F57">
         <v>5</v>
@@ -3977,22 +4427,28 @@
       <c r="G57">
         <v>6</v>
       </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H57" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="I57" s="2" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B58" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C58" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D58" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="E58" t="s">
-        <v>452</v>
+        <v>445</v>
       </c>
       <c r="F58">
         <v>5</v>
@@ -4000,22 +4456,28 @@
       <c r="G58">
         <v>6</v>
       </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H58" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="I58" s="2" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B59" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C59" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="D59" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="E59" t="s">
-        <v>451</v>
+        <v>444</v>
       </c>
       <c r="F59">
         <v>5</v>
@@ -4023,22 +4485,28 @@
       <c r="G59">
         <v>6</v>
       </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H59" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="I59" s="2" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B60" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C60" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="D60" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="E60" t="s">
-        <v>450</v>
+        <v>443</v>
       </c>
       <c r="F60">
         <v>5</v>
@@ -4046,22 +4514,28 @@
       <c r="G60">
         <v>6</v>
       </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H60" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="I60" s="2" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B61" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C61" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D61" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="E61" t="s">
-        <v>449</v>
+        <v>442</v>
       </c>
       <c r="F61">
         <v>5</v>
@@ -4069,22 +4543,28 @@
       <c r="G61">
         <v>6</v>
       </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H61" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="I61" s="2" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B62" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C62" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D62" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="E62" t="s">
-        <v>448</v>
+        <v>441</v>
       </c>
       <c r="F62">
         <v>5</v>
@@ -4092,22 +4572,28 @@
       <c r="G62">
         <v>6</v>
       </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H62" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="I62" s="2" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B63" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C63" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="D63" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="E63" t="s">
-        <v>447</v>
+        <v>440</v>
       </c>
       <c r="F63">
         <v>5</v>
@@ -4115,22 +4601,28 @@
       <c r="G63">
         <v>6</v>
       </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H63" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="I63" s="2" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B64" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C64" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="D64" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="E64" t="s">
-        <v>446</v>
+        <v>439</v>
       </c>
       <c r="F64">
         <v>5</v>
@@ -4138,22 +4630,28 @@
       <c r="G64">
         <v>6</v>
       </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H64" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="I64" s="2" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B65" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C65" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D65" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="E65" t="s">
-        <v>445</v>
+        <v>438</v>
       </c>
       <c r="F65">
         <v>9</v>
@@ -4161,22 +4659,28 @@
       <c r="G65">
         <v>10</v>
       </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H65" t="s">
+        <v>513</v>
+      </c>
+      <c r="I65" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B66" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C66" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D66" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="E66" t="s">
-        <v>444</v>
+        <v>437</v>
       </c>
       <c r="F66">
         <v>9</v>
@@ -4184,22 +4688,28 @@
       <c r="G66">
         <v>10</v>
       </c>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H66" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="I66" s="2" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B67" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C67" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="D67" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="E67" t="s">
-        <v>443</v>
+        <v>436</v>
       </c>
       <c r="F67">
         <v>9</v>
@@ -4207,22 +4717,28 @@
       <c r="G67">
         <v>10</v>
       </c>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H67" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="I67" s="2" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B68" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C68" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="D68" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="E68" t="s">
-        <v>442</v>
+        <v>435</v>
       </c>
       <c r="F68">
         <v>9</v>
@@ -4230,22 +4746,28 @@
       <c r="G68">
         <v>10</v>
       </c>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H68" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="I68" s="2" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B69" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C69" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D69" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="E69" t="s">
-        <v>441</v>
+        <v>434</v>
       </c>
       <c r="F69">
         <v>9</v>
@@ -4253,22 +4775,28 @@
       <c r="G69">
         <v>10</v>
       </c>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H69" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="I69" s="2" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B70" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C70" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="D70" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="E70" t="s">
-        <v>440</v>
+        <v>433</v>
       </c>
       <c r="F70">
         <v>9</v>
@@ -4276,22 +4804,28 @@
       <c r="G70">
         <v>10</v>
       </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H70" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="I70" s="2" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B71" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C71" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="D71" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="E71" t="s">
-        <v>439</v>
+        <v>432</v>
       </c>
       <c r="F71">
         <v>9</v>
@@ -4299,22 +4833,28 @@
       <c r="G71">
         <v>10</v>
       </c>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H71" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="I71" s="2" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B72" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C72" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D72" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="E72" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="F72">
         <v>9</v>
@@ -4322,22 +4862,28 @@
       <c r="G72">
         <v>10</v>
       </c>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H72" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="I72" s="2" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B73" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C73" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="D73" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="E73" t="s">
-        <v>432</v>
+        <v>425</v>
       </c>
       <c r="F73">
         <v>9</v>
@@ -4345,22 +4891,28 @@
       <c r="G73">
         <v>10</v>
       </c>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H73" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="I73" s="2" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B74" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C74" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D74" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="E74" t="s">
-        <v>431</v>
+        <v>424</v>
       </c>
       <c r="F74">
         <v>9</v>
@@ -4368,22 +4920,28 @@
       <c r="G74">
         <v>10</v>
       </c>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H74" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="I74" s="2" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B75" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C75" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="D75" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="E75" t="s">
-        <v>430</v>
+        <v>423</v>
       </c>
       <c r="F75">
         <v>9</v>
@@ -4391,22 +4949,28 @@
       <c r="G75">
         <v>10</v>
       </c>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H75" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="I75" s="2" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B76" t="s">
-        <v>373</v>
+        <v>490</v>
       </c>
       <c r="C76" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="D76" t="s">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="E76" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="F76">
         <v>9</v>
@@ -4414,22 +4978,28 @@
       <c r="G76">
         <v>10</v>
       </c>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H76" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="I76" s="2" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B77" t="s">
         <v>24</v>
       </c>
       <c r="C77" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="D77" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E77" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="F77">
         <v>7</v>
@@ -4437,22 +5007,28 @@
       <c r="G77">
         <v>8</v>
       </c>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H77" t="s">
+        <v>515</v>
+      </c>
+      <c r="I77" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="B78" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C78" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="D78" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="E78" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
       <c r="F78">
         <v>7</v>
@@ -4460,22 +5036,28 @@
       <c r="G78">
         <v>8</v>
       </c>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H78" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="I78" s="2" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="B79" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C79" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="D79" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="E79" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
       <c r="F79">
         <v>7</v>
@@ -4483,22 +5065,28 @@
       <c r="G79">
         <v>8</v>
       </c>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H79" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="I79" s="2" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="B80" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C80" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="D80" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="E80" t="s">
-        <v>425</v>
+        <v>418</v>
       </c>
       <c r="F80">
         <v>7</v>
@@ -4506,22 +5094,28 @@
       <c r="G80">
         <v>8</v>
       </c>
-    </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H80" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="I80" s="2" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="B81" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C81" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="D81" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="E81" t="s">
-        <v>423</v>
+        <v>416</v>
       </c>
       <c r="F81">
         <v>7</v>
@@ -4529,22 +5123,28 @@
       <c r="G81">
         <v>8</v>
       </c>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H81" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="I81" s="2" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="B82" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C82" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="D82" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="E82" t="s">
-        <v>424</v>
+        <v>417</v>
       </c>
       <c r="F82">
         <v>7</v>
@@ -4552,22 +5152,28 @@
       <c r="G82">
         <v>8</v>
       </c>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H82" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="I82" s="2" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
+        <v>168</v>
+      </c>
+      <c r="B83" t="s">
+        <v>488</v>
+      </c>
+      <c r="C83" t="s">
         <v>172</v>
       </c>
-      <c r="B83" t="s">
-        <v>81</v>
-      </c>
-      <c r="C83" t="s">
-        <v>176</v>
-      </c>
       <c r="D83" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="E83" t="s">
-        <v>422</v>
+        <v>415</v>
       </c>
       <c r="F83">
         <v>7</v>
@@ -4575,22 +5181,28 @@
       <c r="G83">
         <v>8</v>
       </c>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H83" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="I83" s="2" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="B84" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C84" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="D84" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="E84" t="s">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="F84">
         <v>7</v>
@@ -4598,22 +5210,28 @@
       <c r="G84">
         <v>8</v>
       </c>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H84" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="I84" s="2" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="B85" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C85" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="D85" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="E85" t="s">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="F85">
         <v>7</v>
@@ -4621,22 +5239,28 @@
       <c r="G85">
         <v>8</v>
       </c>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H85" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="I85" s="2" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="B86" t="s">
-        <v>84</v>
+        <v>487</v>
       </c>
       <c r="C86" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="D86" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="E86" t="s">
-        <v>419</v>
+        <v>412</v>
       </c>
       <c r="F86">
         <v>7</v>
@@ -4644,22 +5268,28 @@
       <c r="G86">
         <v>8</v>
       </c>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H86" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="I86" s="2" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="B87" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C87" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="D87" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="E87" t="s">
-        <v>418</v>
+        <v>411</v>
       </c>
       <c r="F87">
         <v>7</v>
@@ -4667,22 +5297,28 @@
       <c r="G87">
         <v>8</v>
       </c>
-    </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H87" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="I87" s="2" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="B88" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C88" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="D88" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="E88" t="s">
-        <v>417</v>
+        <v>410</v>
       </c>
       <c r="F88">
         <v>7</v>
@@ -4690,22 +5326,28 @@
       <c r="G88">
         <v>8</v>
       </c>
-    </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H88" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="I88" s="2" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="B89" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C89" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="D89" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="E89" t="s">
-        <v>416</v>
+        <v>409</v>
       </c>
       <c r="F89">
         <v>7</v>
@@ -4713,22 +5355,28 @@
       <c r="G89">
         <v>8</v>
       </c>
-    </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H89" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="I89" s="2" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="B90" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C90" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="D90" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="E90" t="s">
-        <v>415</v>
+        <v>408</v>
       </c>
       <c r="F90">
         <v>7</v>
@@ -4736,22 +5384,28 @@
       <c r="G90">
         <v>8</v>
       </c>
-    </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H90" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="I90" s="2" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="B91" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C91" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="D91" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="E91" t="s">
-        <v>414</v>
+        <v>407</v>
       </c>
       <c r="F91">
         <v>7</v>
@@ -4759,22 +5413,28 @@
       <c r="G91">
         <v>8</v>
       </c>
-    </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H91" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="I91" s="2" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="B92" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C92" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="D92" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="E92" t="s">
-        <v>413</v>
+        <v>406</v>
       </c>
       <c r="F92">
         <v>7</v>
@@ -4782,22 +5442,28 @@
       <c r="G92">
         <v>8</v>
       </c>
-    </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H92" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="I92" s="2" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="B93" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C93" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="D93" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="E93" t="s">
-        <v>412</v>
+        <v>405</v>
       </c>
       <c r="F93">
         <v>7</v>
@@ -4805,22 +5471,28 @@
       <c r="G93">
         <v>8</v>
       </c>
-    </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H93" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="I93" s="2" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="B94" t="s">
         <v>3</v>
       </c>
       <c r="C94" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="D94" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="E94" t="s">
-        <v>411</v>
+        <v>404</v>
       </c>
       <c r="F94">
         <v>7</v>
@@ -4828,22 +5500,28 @@
       <c r="G94">
         <v>8</v>
       </c>
-    </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H94" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="I94" s="2" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="B95" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C95" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="D95" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="E95" t="s">
-        <v>406</v>
+        <v>399</v>
       </c>
       <c r="F95">
         <v>7</v>
@@ -4851,22 +5529,28 @@
       <c r="G95">
         <v>8</v>
       </c>
-    </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H95" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="I95" s="2" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="B96" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C96" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="D96" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="E96" t="s">
-        <v>405</v>
+        <v>398</v>
       </c>
       <c r="F96">
         <v>7</v>
@@ -4874,22 +5558,28 @@
       <c r="G96">
         <v>8</v>
       </c>
-    </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H96" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="I96" s="2" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="B97" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C97" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="D97" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="E97" t="s">
-        <v>404</v>
+        <v>397</v>
       </c>
       <c r="F97">
         <v>7</v>
@@ -4897,22 +5587,28 @@
       <c r="G97">
         <v>8</v>
       </c>
-    </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H97" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="I97" s="2" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="B98" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C98" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="D98" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="E98" t="s">
-        <v>403</v>
+        <v>396</v>
       </c>
       <c r="F98">
         <v>7</v>
@@ -4920,28 +5616,115 @@
       <c r="G98">
         <v>8</v>
       </c>
-    </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H98" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="I98" s="2" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="B99" t="s">
-        <v>377</v>
+        <v>492</v>
       </c>
       <c r="C99" t="s">
-        <v>378</v>
+        <v>371</v>
       </c>
       <c r="D99" t="s">
-        <v>379</v>
+        <v>372</v>
       </c>
       <c r="E99" t="s">
-        <v>402</v>
+        <v>395</v>
       </c>
       <c r="F99">
         <v>7</v>
       </c>
       <c r="G99">
         <v>8</v>
+      </c>
+      <c r="H99" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="I99" s="2" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A100" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="B100" t="s">
+        <v>493</v>
+      </c>
+      <c r="C100" t="s">
+        <v>496</v>
+      </c>
+      <c r="D100" t="s">
+        <v>499</v>
+      </c>
+      <c r="E100" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="F100" s="2">
+        <v>7</v>
+      </c>
+      <c r="G100" s="2">
+        <v>8</v>
+      </c>
+      <c r="H100" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="I100" s="2" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A101" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="B101" t="s">
+        <v>494</v>
+      </c>
+      <c r="C101" t="s">
+        <v>497</v>
+      </c>
+      <c r="D101" t="s">
+        <v>500</v>
+      </c>
+      <c r="E101" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="F101">
+        <v>11</v>
+      </c>
+      <c r="G101">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A102" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="B102" t="s">
+        <v>495</v>
+      </c>
+      <c r="C102" t="s">
+        <v>498</v>
+      </c>
+      <c r="D102" t="s">
+        <v>501</v>
+      </c>
+      <c r="E102" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="F102">
+        <v>11</v>
+      </c>
+      <c r="G102">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
